--- a/task261/golden/retirement_segments_2027.xlsx
+++ b/task261/golden/retirement_segments_2027.xlsx
@@ -145,7 +145,7 @@
     <t>Each difference's standard error is taken from the difference itself, recomputed on every replicate weight and implicate. Committee's rule: neighbouring groups are kept apart where the difference is more than 1.96 times its standard error.</t>
   </si>
   <si>
-    <t>Our book: client register and annuity listing pulled 12 January 2027; pension extract and nominations at 31 December 2026. A pension whose member died before 31 December with a reversionary nominated is counted with the survivor; annuity income is the annual rate at 31 December 2026, deferred annuities not yet paying left out.</t>
+    <t>Our book: client register and annuity listing pulled 12 January 2027; pension extract and nominations at 31 December 2026. A pension whose member died before 31 December with a reversionary nominated is counted with the survivor; a partner whose 2026 death the annuity listing records is not counted, though the register still holds them; a member's pensions that repeat one balance and payment count once; annuity income is the annual rate at 31 December 2026, deferred annuities not yet paying left out.</t>
   </si>
   <si>
     <t>Dollar figures rounded to the nearest thousand.</t>
@@ -920,19 +920,19 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C2" s="4">
-        <v>207655000</v>
+        <v>210509000</v>
       </c>
       <c r="D2" s="4">
-        <v>11448000</v>
+        <v>11589000</v>
       </c>
       <c r="E2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F2" s="4">
-        <v>3606000</v>
+        <v>3653000</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -940,19 +940,19 @@
         <v>17</v>
       </c>
       <c r="B3" s="4">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="C3" s="4">
-        <v>520479000</v>
+        <v>521126000</v>
       </c>
       <c r="D3" s="4">
-        <v>30320000</v>
+        <v>30350000</v>
       </c>
       <c r="E3">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F3" s="4">
-        <v>9011000</v>
+        <v>9041000</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -960,19 +960,19 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C4" s="4">
-        <v>249568000</v>
+        <v>249685000</v>
       </c>
       <c r="D4" s="4">
-        <v>17994000</v>
+        <v>18003000</v>
       </c>
       <c r="E4">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F4" s="4">
-        <v>5614000</v>
+        <v>5510000</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -983,16 +983,16 @@
         <v>2356</v>
       </c>
       <c r="C5" s="6">
-        <v>977702000</v>
+        <v>981320000</v>
       </c>
       <c r="D5" s="6">
-        <v>59762000</v>
+        <v>59942000</v>
       </c>
       <c r="E5" s="2">
         <v>927</v>
       </c>
       <c r="F5" s="6">
-        <v>18231000</v>
+        <v>18204000</v>
       </c>
     </row>
   </sheetData>
